--- a/reports/weekly_report_2026-06-08.xlsx
+++ b/reports/weekly_report_2026-06-08.xlsx
@@ -34,12 +34,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -79,7 +79,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -88,7 +89,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,12 +454,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -471,158 +471,237 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>统计周期</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-08 ~ 2026-06-14</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>筛选条件</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>统计周期</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>上周</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-08 ~ 2026-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>园区筛选</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>全部园区</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>数据覆盖</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0 条记录, 覆盖 0 个园区 (范围内总计 0 条)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>生成时间</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-20T10:09:54.712723</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-20T10:52:56.971781</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>导出文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>E:\work\d017\reports\weekly_report_2026-06-08.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>E:\work\d017\reports\weekly_report_2026-06-08.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>指标</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>发布总数</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>次</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>本周发布申请总数</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>成功发布</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>次</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>全量发布成功的次数</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>回滚次数</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>次</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>触发熔断或手动回滚次数</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>发布成功率</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>成功发布 / 总发布</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>平均审批时长</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>分钟</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>从提交审批到通过的平均时间</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="8">
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -642,41 +721,41 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>按发布类型统计</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>发布类型</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>HOTFIX</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -702,19 +781,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>按园区发布统计</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>园区ID</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>发布次数</t>
         </is>
@@ -734,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -744,32 +823,144 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>每日发布趋势</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>总发布数</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>成功发布</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>回滚数</t>
         </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
